--- a/data/parameter_to_latex.xlsx
+++ b/data/parameter_to_latex.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LEHOUX\Maquereau\iml-mackerel\00.0_model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1AF213-03BB-4878-9B40-5E7101F26231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD02084-3962-478C-9C20-AD17D4F30B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6510" yWindow="1965" windowWidth="19425" windowHeight="10425" xr2:uid="{F6A7D8AD-B35F-4017-889A-937D0D1DD344}"/>
+    <workbookView xWindow="5496" yWindow="1236" windowWidth="17280" windowHeight="8880" xr2:uid="{F6A7D8AD-B35F-4017-889A-937D0D1DD344}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>logFpar_0</t>
   </si>
@@ -126,6 +126,30 @@
   </si>
   <si>
     <t>Parameter</t>
+  </si>
+  <si>
+    <t>$$q $$</t>
+  </si>
+  <si>
+    <t>$$Sel_a $$</t>
+  </si>
+  <si>
+    <t>$$\alpha $$</t>
+  </si>
+  <si>
+    <t>$$\beta $$</t>
+  </si>
+  <si>
+    <t>$$\sigma^2_N $$</t>
+  </si>
+  <si>
+    <t>$$\sigma^2_{cp_a} $$</t>
+  </si>
+  <si>
+    <t>$$ \sigma^2_{s} $$</t>
+  </si>
+  <si>
+    <t>Parameter output</t>
   </si>
 </sst>
 </file>
@@ -181,9 +205,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -221,7 +245,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -327,7 +351,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -469,7 +493,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -477,135 +501,183 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5750E470-94D7-42C3-A443-90BD8048F434}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.5546875" customWidth="1"/>
+    <col min="3" max="3" width="41.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>28</v>
       </c>
       <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>